--- a/output/pdf_financials_xlsx/AKT.A.xlsx
+++ b/output/pdf_financials_xlsx/AKT.A.xlsx
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.814</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.773</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>20.133</v>
+        <v>18.319</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>11.901</v>
+        <v>11.377</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>8.51</v>
+        <v>7.737</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>36.8</v>
+        <v>34.986</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>29.377</v>
+        <v>28.853</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>8.53454</v>
+        <v>7.76154</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>26.81316759686985</v>
+        <v>25.4914533028285</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>27.64555866105794</v>
+        <v>27.15244252467933</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>7.679711331671631</v>
+        <v>6.984135839684696</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -28288,7 +28288,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E299" s="5" t="n">

--- a/output/pdf_financials_xlsx/AKT.A.xlsx
+++ b/output/pdf_financials_xlsx/AKT.A.xlsx
@@ -2338,16 +2338,16 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>41.534</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>28.523</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>0.028523</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>0.033339</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>2.948</v>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>0.02822</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>0.027024</v>
       </c>
       <c r="K37" s="1" t="inlineStr">
         <is>
@@ -2534,16 +2534,16 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>41.534</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>28.523</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>0.028523</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>0.033339</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>2.948</v>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>0.02822</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>0.027024</v>
       </c>
       <c r="K41" s="1" t="inlineStr">
         <is>
@@ -2880,16 +2880,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>42.657</v>
+        <v>1.123</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>47.274</v>
+        <v>18.751</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.047274</v>
+        <v>0.018751</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.043561</v>
+        <v>0.010222</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.03065</v>
+        <v>0.00243</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.030189</v>
+        <v>0.003165</v>
       </c>
       <c r="K48" s="1" t="inlineStr">
         <is>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>0</v>
+        <v>153.044</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0</v>
+        <v>147.799</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>0.121346</v>
@@ -6804,10 +6804,10 @@
         </is>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>-0.0061</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>0</v>
+        <v>-0.0061</v>
       </c>
       <c r="K126" s="1" t="inlineStr">
         <is>
@@ -7224,10 +7224,10 @@
         </is>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.013193</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.020569</v>
       </c>
       <c r="K134" s="1" t="inlineStr">
         <is>
@@ -7274,10 +7274,10 @@
         </is>
       </c>
       <c r="I135" s="3" t="n">
-        <v>0.011892</v>
+        <v>-0.001301</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>0.005074</v>
+        <v>-0.015495</v>
       </c>
       <c r="K135" s="1" t="inlineStr">
         <is>
@@ -8659,7 +8659,11 @@
           <t>Accounts receivable Note 12</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -8937,7 +8941,11 @@
           <t>Restricted cash Note 10</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -9367,7 +9375,11 @@
           <t>Dividends payable Note 15</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DividendsPayable</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -14243,7 +14255,11 @@
           <t>Accounts receivable Note 23 48,351</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -14460,7 +14476,11 @@
           <t>Restricted cash Note 7 3,000</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -17994,7 +18014,11 @@
           <t>Accounts receivable Note 13</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -18280,7 +18304,11 @@
           <t>Restricted cash Note 16</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -18349,7 +18377,11 @@
           <t>Capital assets Note 2</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -19424,7 +19456,11 @@
           <t>Accounts receivable Note 14</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E173" s="5" t="n">
         <v>41.534</v>
       </c>
@@ -19562,7 +19598,11 @@
           <t>Restricted cash Note 17</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E175" s="5" t="n">
         <v>5</v>
       </c>
@@ -19631,7 +19671,11 @@
           <t>Capital assets Note 2</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E176" s="5" t="n">
         <v>153.044</v>
       </c>
@@ -21400,7 +21444,11 @@
           <t>Capital expenditures Note 8</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -21822,7 +21870,11 @@
           <t>Dividends paid Note 15</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AKT.A.xlsx
+++ b/output/pdf_financials_xlsx/AKT.A.xlsx
@@ -1631,15 +1631,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="3" t="n">
+        <v>0.005329</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>-0.039177</v>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
@@ -3855,25 +3851,19 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016338</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1.799</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0.001431</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0.211</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="J67" s="3" t="n">
         <v>0</v>
@@ -3907,18 +3897,14 @@
       <c r="E68" s="3" t="n">
         <v>0.01883</v>
       </c>
-      <c r="F68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F68" s="3" t="n">
+        <v>1.799</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0.001431</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>1.872</v>
+        <v>2.083</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>0.008468</v>
@@ -5449,15 +5435,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="3" t="n">
+        <v>0.005329</v>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>-0.039177</v>
       </c>
       <c r="K99" s="1" t="inlineStr">
         <is>
@@ -20322,7 +20304,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -20535,7 +20521,11 @@
           <t>Deferred income tax expense (recovery) Note 6</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -24590,7 +24580,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E245" s="5" t="n">
         <v>3.763</v>
       </c>
